--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484860_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484860_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.929</v>
+        <v>-2.6953</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6566</v>
+        <v>-0.4617</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2724</v>
+        <v>-2.2336</v>
       </c>
       <c r="G2" t="n">
         <v>-1.8996</v>
@@ -610,13 +610,13 @@
         <v>1.1322</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7255</v>
+        <v>-0.0408</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4551</v>
+        <v>-0.2602</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1806</v>
+        <v>0.2194</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.0996</v>
+        <v>-3.6229</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3125</v>
+        <v>-0.9945000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.7871</v>
+        <v>-2.6284</v>
       </c>
       <c r="G3" t="n">
         <v>-5.9247</v>
@@ -688,13 +688,13 @@
         <v>0.9435</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6748</v>
+        <v>0.1515</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0328</v>
+        <v>0.3507</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3579</v>
+        <v>-0.1992</v>
       </c>
       <c r="V3" t="n">
         <v>4.9808</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. TERREROS RIVAS</t>
+          <t>D. ALFEREZ CANSECO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.4638</v>
+        <v>-3.9289</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5582</v>
+        <v>-2.7503</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.022</v>
+        <v>-1.1786</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4593</v>
+        <v>-2.5964</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0368</v>
+        <v>-1.6419</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4961</v>
+        <v>-0.9545</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1495</v>
+        <v>-0.8354</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4675</v>
+        <v>-0.227</v>
       </c>
       <c r="L4" t="n">
-        <v>2.682</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.6902</v>
+        <v>-1.761</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.5043</v>
+        <v>-1.4149</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.1859</v>
+        <v>-0.3461</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.9627</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.661</v>
+        <v>-1.887</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6983</v>
+        <v>1.1322</v>
       </c>
       <c r="S4" t="n">
-        <v>0.964</v>
+        <v>-0.5777</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4472</v>
+        <v>-0.3297</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4831</v>
+        <v>-0.248</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9244</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6226</v>
+        <v>0.3018</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.547</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. ALFEREZ CANSECO</t>
+          <t>M. DAMESTOY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.4064</v>
+        <v>-4.3813</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.0426</v>
+        <v>-3.3348</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3638</v>
+        <v>-1.0464</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.5964</v>
+        <v>-1.2373</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6419</v>
+        <v>-1.4971</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9545</v>
+        <v>0.2598</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8354</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.227</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6084000000000001</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.761</v>
+        <v>-0.6511</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4149</v>
+        <v>-0.9109</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3461</v>
+        <v>0.2598</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7548</v>
+        <v>-2.4531</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1322</v>
+        <v>0.3774</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0552</v>
+        <v>0.2335</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.622</v>
+        <v>0.0818</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4332</v>
+        <v>0.1517</v>
       </c>
       <c r="V5" t="n">
+        <v>-0.9244</v>
+      </c>
+      <c r="W5" t="n">
         <v>0</v>
       </c>
-      <c r="W5" t="n">
-        <v>0.3018</v>
-      </c>
       <c r="X5" t="n">
-        <v>-0.3018</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. DAMESTOY</t>
+          <t>B. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.6736</v>
+        <v>-4.6599</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.6271</v>
+        <v>0.2916</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0464</v>
+        <v>-4.9515</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2373</v>
+        <v>0.4593</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4971</v>
+        <v>-0.0368</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2598</v>
+        <v>0.4961</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5862000000000001</v>
+        <v>5.1495</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5862000000000001</v>
+        <v>2.4675</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.682</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6511</v>
+        <v>-4.6902</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9109</v>
+        <v>-2.5043</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2598</v>
+        <v>-2.1859</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.4531</v>
+        <v>-3.9627</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8305</v>
+        <v>-5.661</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3774</v>
+        <v>1.6983</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0588</v>
+        <v>-0.2321</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2105</v>
+        <v>0.1805</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1517</v>
+        <v>-0.4126</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9244</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.9244</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.4949</v>
+        <v>-5.3265</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.215</v>
+        <v>-3.0201</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2799</v>
+        <v>-2.3064</v>
       </c>
       <c r="G7" t="n">
         <v>-6.4308</v>
@@ -1000,13 +1000,13 @@
         <v>0.9435</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6302</v>
+        <v>-0.4618</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6808</v>
+        <v>-0.4859</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0506</v>
+        <v>0.0241</v>
       </c>
       <c r="V7" t="n">
         <v>0.6226</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. GARCIA CARCASES</t>
+          <t>I. ALAMINOS HERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.9173</v>
+        <v>-5.3737</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6753</v>
+        <v>-1.1758</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.5926</v>
+        <v>-4.1979</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5895</v>
+        <v>-4.1454</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4203</v>
+        <v>-2.1647</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1692</v>
+        <v>-1.9808</v>
       </c>
       <c r="J8" t="n">
-        <v>3.0835</v>
+        <v>0.0246</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1574</v>
+        <v>-0.1158</v>
       </c>
       <c r="L8" t="n">
-        <v>1.9261</v>
+        <v>0.1404</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.673</v>
+        <v>-4.17</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5777</v>
+        <v>-2.0488</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.0953</v>
+        <v>-2.1212</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1887</v>
+        <v>0.1887</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6983</v>
+        <v>1.1322</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3279</v>
+        <v>-0.4926</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.823</v>
+        <v>-0.2569</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5049</v>
+        <v>-0.2357</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.8112</v>
+        <v>-0.9244</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.113</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. ALAMINOS HERNANDEZ</t>
+          <t>G. GARCIA CARCASES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.0545</v>
+        <v>-5.5011</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5656</v>
+        <v>1.065</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.4889</v>
+        <v>-6.5661</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.1454</v>
+        <v>-1.5895</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1647</v>
+        <v>-0.4203</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9808</v>
+        <v>-1.1692</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0246</v>
+        <v>3.0835</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1158</v>
+        <v>1.1574</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1404</v>
+        <v>1.9261</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.17</v>
+        <v>-4.673</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.0488</v>
+        <v>-1.5777</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.1212</v>
+        <v>-3.0953</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1887</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1322</v>
+        <v>1.6983</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1733</v>
+        <v>-0.9117</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.4333</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.4785</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9244</v>
+        <v>-2.8112</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9244</v>
+        <v>-3.113</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.1336</v>
+        <v>-5.8426</v>
       </c>
       <c r="E10" t="n">
         <v>-2.8198</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.3138</v>
+        <v>-3.0228</v>
       </c>
       <c r="G10" t="n">
         <v>-3.031</v>
@@ -1234,13 +1234,13 @@
         <v>0.9435</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2539</v>
+        <v>-0.9629</v>
       </c>
       <c r="T10" t="n">
         <v>-0.2664</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9875</v>
+        <v>-0.6965</v>
       </c>
       <c r="V10" t="n">
         <v>-2.7922</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.6328</v>
+        <v>-7.385</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1539</v>
+        <v>-2.9591</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.4788</v>
+        <v>-4.4259</v>
       </c>
       <c r="G11" t="n">
         <v>-2.406</v>
@@ -1312,13 +1312,13 @@
         <v>0.3774</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2268</v>
+        <v>-0.9791</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6808</v>
+        <v>-0.4859</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5461</v>
+        <v>-0.4932</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4904</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-48.80550000000001</v>
+        <v>-48.71719999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-16.1596</v>
+        <v>-16.1595</v>
       </c>
       <c r="F12" t="n">
-        <v>-32.6457</v>
+        <v>-32.5576</v>
       </c>
       <c r="G12" t="n">
         <v>-28.8014</v>
@@ -1363,7 +1363,7 @@
         <v>-17.1016</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01279999999999926</v>
+        <v>0.0127999999999997</v>
       </c>
       <c r="K12" t="n">
         <v>2.6137</v>
@@ -1390,13 +1390,13 @@
         <v>10.3785</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.3618</v>
+        <v>-4.2737</v>
       </c>
       <c r="T12" t="n">
         <v>-1.9053</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.4565</v>
+        <v>-2.3685</v>
       </c>
       <c r="V12" t="n">
         <v>-5.2636</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.813</v>
+        <v>11.8659</v>
       </c>
       <c r="E13" t="n">
-        <v>7.7849</v>
+        <v>7.3951</v>
       </c>
       <c r="F13" t="n">
-        <v>4.0282</v>
+        <v>4.4708</v>
       </c>
       <c r="G13" t="n">
         <v>7.7484</v>
@@ -1468,13 +1468,13 @@
         <v>2.4531</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3097</v>
+        <v>1.3626</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7483</v>
+        <v>0.3585</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5615</v>
+        <v>1.0041</v>
       </c>
       <c r="V13" t="n">
         <v>0.3018</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.7203</v>
+        <v>9.795999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>9.3033</v>
+        <v>9.010999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.417</v>
+        <v>0.785</v>
       </c>
       <c r="G14" t="n">
         <v>4.2693</v>
@@ -1546,13 +1546,13 @@
         <v>2.0757</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0394</v>
+        <v>0.0363</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5472</v>
+        <v>0.2549</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5866</v>
+        <v>-0.2186</v>
       </c>
       <c r="V14" t="n">
         <v>4.3582</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.173</v>
+        <v>7.5669</v>
       </c>
       <c r="E15" t="n">
-        <v>6.273</v>
+        <v>5.8832</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9</v>
+        <v>1.6837</v>
       </c>
       <c r="G15" t="n">
         <v>3.734</v>
@@ -1624,13 +1624,13 @@
         <v>1.6983</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4955</v>
+        <v>0.8894</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7947</v>
+        <v>0.405</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7008</v>
+        <v>0.4845</v>
       </c>
       <c r="V15" t="n">
         <v>1.2452</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.1398</v>
+        <v>7.1181</v>
       </c>
       <c r="E16" t="n">
-        <v>5.7396</v>
+        <v>5.3498</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4002</v>
+        <v>1.7682</v>
       </c>
       <c r="G16" t="n">
         <v>6.0301</v>
@@ -1702,13 +1702,13 @@
         <v>2.2644</v>
       </c>
       <c r="S16" t="n">
-        <v>1.034</v>
+        <v>1.0123</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9711</v>
+        <v>0.5813</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0629</v>
+        <v>0.4309</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2452</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ZURBRIGGEN</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.7645</v>
+        <v>4.787</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3807</v>
+        <v>2.4211</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3838</v>
+        <v>2.3659</v>
       </c>
       <c r="G17" t="n">
-        <v>0.07580000000000001</v>
+        <v>2.6927</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1144</v>
+        <v>1.1989</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1902</v>
+        <v>1.4937</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4255</v>
+        <v>2.098</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0892</v>
+        <v>0.5181</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5148</v>
+        <v>1.58</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3497</v>
+        <v>0.5946</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0252</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3245</v>
+        <v>-0.0863</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1322</v>
+        <v>0.5661</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6418</v>
+        <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4061</v>
+        <v>0.283</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3144</v>
+        <v>0.0214</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0917</v>
+        <v>0.2616</v>
       </c>
       <c r="V17" t="n">
-        <v>3.4148</v>
+        <v>1.2452</v>
       </c>
       <c r="W17" t="n">
-        <v>3.4148</v>
+        <v>1.2452</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.8039</v>
+        <v>4.1792</v>
       </c>
       <c r="E18" t="n">
-        <v>1.798</v>
+        <v>1.9929</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0058</v>
+        <v>2.1863</v>
       </c>
       <c r="G18" t="n">
         <v>2.1539</v>
@@ -1858,13 +1858,13 @@
         <v>2.4531</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4421</v>
+        <v>0.8174</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0312</v>
+        <v>0.1637</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4733</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2452</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>A. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.4423</v>
+        <v>3.8865</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8365</v>
+        <v>1.7961</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6058</v>
+        <v>2.0905</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6927</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1989</v>
+        <v>-1.1144</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4937</v>
+        <v>1.1902</v>
       </c>
       <c r="J19" t="n">
-        <v>2.098</v>
+        <v>1.4255</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5181</v>
+        <v>-0.0892</v>
       </c>
       <c r="L19" t="n">
-        <v>1.58</v>
+        <v>1.5148</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5946</v>
+        <v>-1.3497</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6808999999999999</v>
+        <v>-1.0252</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0863</v>
+        <v>-0.3245</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5661</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9435</v>
+        <v>-3.774</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5096</v>
+        <v>2.6418</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0617</v>
+        <v>1.5281</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5632</v>
+        <v>0.7298</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4985</v>
+        <v>0.7984</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2452</v>
+        <v>3.4148</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2452</v>
+        <v>3.4148</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8662</v>
+        <v>1.731</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1338</v>
+        <v>1.8158</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2676</v>
+        <v>-0.0848</v>
       </c>
       <c r="G20" t="n">
         <v>3.0688</v>
@@ -2014,13 +2014,13 @@
         <v>2.4531</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5802</v>
+        <v>0.2847</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.622</v>
+        <v>0.0601</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0418</v>
+        <v>0.2246</v>
       </c>
       <c r="V20" t="n">
         <v>-2.1886</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2034</v>
+        <v>0.5403</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6584</v>
+        <v>-0.2686</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8618</v>
+        <v>0.8089</v>
       </c>
       <c r="G21" t="n">
         <v>0.1335</v>
@@ -2092,13 +2092,13 @@
         <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3074</v>
+        <v>0.0294</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4703</v>
+        <v>-0.0806</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1629</v>
+        <v>0.11</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.121</v>
+        <v>-0.7169</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7004</v>
+        <v>-1.5055</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5793</v>
+        <v>0.7886</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1051</v>
@@ -2170,13 +2170,13 @@
         <v>1.887</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3368</v>
+        <v>0.0673</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2323</v>
+        <v>-0.0374</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1046</v>
+        <v>0.1047</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6226</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>48.8054</v>
+        <v>50.754</v>
       </c>
       <c r="E23" t="n">
-        <v>33.891</v>
+        <v>33.8909</v>
       </c>
       <c r="F23" t="n">
-        <v>14.9143</v>
+        <v>16.8631</v>
       </c>
       <c r="G23" t="n">
         <v>28.8014</v>
@@ -2230,7 +2230,7 @@
         <v>14.5006</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.01279999999999992</v>
+        <v>-0.01280000000000014</v>
       </c>
       <c r="N23" t="n">
         <v>-2.6138</v>
@@ -2248,13 +2248,13 @@
         <v>20.75700000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>4.361899999999999</v>
+        <v>6.3105</v>
       </c>
       <c r="T23" t="n">
         <v>2.4567</v>
       </c>
       <c r="U23" t="n">
-        <v>1.9052</v>
+        <v>3.853899999999999</v>
       </c>
       <c r="V23" t="n">
         <v>5.2636</v>
